--- a/jogos_2025-05-15.xlsx
+++ b/jogos_2025-05-15.xlsx
@@ -762,33 +762,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.39</v>
+        <v>2.86</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="T3" t="n">
-        <v>2.89</v>
+        <v>3.17</v>
       </c>
       <c r="U3" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
         <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AD3" t="n">
         <v>1.91</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>['45+2', '62']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
       <c r="AG3" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45792.41666666666</v>
@@ -891,32 +891,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="M4" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>2.86</v>
+        <v>2.39</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>3.17</v>
+        <v>2.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AD4" t="n">
         <v>1.91</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['45+2', '62']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45792.41666666666</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Havadar</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>2.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="U5" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="X5" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['37', '77', '89']</t>
+          <t>['82', '90+7']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.55</v>
+        <v>4.9</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45792.47916666666</v>
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havadar</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>11</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Z6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['82', '90+7']</t>
+          <t>['37', '77', '89']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.9</v>
+        <v>2.55</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45792.47916666666</v>
@@ -1288,48 +1288,48 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2.85</v>
-      </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.12</v>
+        <v>3.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.55</v>
@@ -1338,59 +1338,59 @@
         <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AB7" t="n">
         <v>1.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['50', '58', '78']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45792.47916666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="P8" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.72</v>
+        <v>4.12</v>
       </c>
       <c r="R8" t="n">
         <v>1.55</v>
@@ -1467,59 +1467,59 @@
         <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="AB8" t="n">
         <v>1.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['50', '58', '78']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45792.47916666666</v>
@@ -1804,103 +1804,103 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>10</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="AB11" t="n">
         <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.18</v>
+        <v>2.4</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,35 +1923,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.75</v>
+        <v>2.47</v>
       </c>
       <c r="M12" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['29', '34', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45792.5</v>
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,77 +2088,77 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>10</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.8</v>
       </c>
-      <c r="M13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.75</v>
+        <v>9.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.58</v>
+        <v>3.95</v>
       </c>
       <c r="AB13" t="n">
         <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2310,35 +2310,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.47</v>
+        <v>4.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '34', '90']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45792.5</v>
@@ -2439,35 +2439,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X16" t="n">
         <v>2.92</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="Y16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.22</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45792.52083333334</v>
@@ -2568,35 +2568,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="N17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.1</v>
       </c>
-      <c r="O17" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45792.52083333334</v>
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>3.85</v>
-      </c>
       <c r="M20" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>4.75</v>
+        <v>2.63</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>2.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['78', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45792.54166666666</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
         <v>12</v>
       </c>
       <c r="O21" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3178,12 +3178,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['25', '34', '64']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AG21" t="n">
@@ -3193,10 +3193,10 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45792.54166666666</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="N22" t="n">
         <v>12</v>
       </c>
       <c r="O22" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['25', '34', '64']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45792.54166666666</v>
@@ -3481,19 +3481,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>3.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="O24" t="n">
-        <v>2.63</v>
+        <v>4.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78', '90+1']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG24" t="n">
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45792.54166666666</v>
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="M27" t="n">
-        <v>3.94</v>
+        <v>3.79</v>
       </c>
       <c r="N27" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V27" t="n">
         <v>1.04</v>
       </c>
       <c r="W27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['7', '11', '63', '82']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['23', '27', '84']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.22</v>
       </c>
-      <c r="X27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AH27" t="n">
         <v>2</v>
       </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AI27" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45792.58333333334</v>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
         <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.75</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['25', '82']</t>
+          <t>['37', '45+6']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '61']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45792.58333333334</v>
@@ -4116,33 +4116,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="M29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA29" t="n">
         <v>3.75</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="AB29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['25', '82']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.28</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
+      <c r="AI29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.26</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45792.58333333334</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,80 +4281,80 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="N30" t="n">
-        <v>3.53</v>
+        <v>3.92</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="T30" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V30" t="n">
         <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X30" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['58', '88']</t>
+          <t>['57', '70']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ30" t="n">
         <v>2.45</v>
@@ -4374,35 +4374,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" t="n">
         <v>5</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.52</v>
-      </c>
       <c r="O31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q31" t="n">
         <v>5.25</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S31" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.95</v>
-      </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="X31" t="n">
-        <v>3.65</v>
+        <v>2.28</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.35</v>
+        <v>6.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['34', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['4', '39']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.48</v>
+        <v>2.75</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45792.58333333334</v>
@@ -4503,119 +4503,119 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O32" t="n">
         <v>2</v>
       </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>3</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.75</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AB32" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AC32" t="n">
         <v>1.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['37', '45+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['51', '61']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.38</v>
+        <v>2.35</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45792.58333333334</v>
@@ -4632,29 +4632,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="M33" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="O33" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="P33" t="n">
         <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U33" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
         <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['57', '70']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AI33" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45792.58333333334</v>
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>2</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.64</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="N35" t="n">
-        <v>4.1</v>
+        <v>1.52</v>
       </c>
       <c r="O35" t="n">
-        <v>2.2</v>
+        <v>5.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="R35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.28</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T35" t="n">
+      <c r="X35" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['34', '79']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['4', '39']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>2.3</v>
       </c>
-      <c r="U35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['7', '11', '63', '82']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['23', '27', '84']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH35" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.55</v>
+        <v>1.48</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45792.58333333334</v>
@@ -5019,29 +5019,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>3.53</v>
       </c>
       <c r="O36" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="P36" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.25</v>
+        <v>3.95</v>
       </c>
       <c r="R36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.62</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['58', '88']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2.45</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45792.58333333334</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>10</v>
+      </c>
+      <c r="M45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O45" t="n">
+        <v>8</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>['53', '90+5']</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
         <v>3.4</v>
       </c>
-      <c r="M45" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O45" t="n">
-        <v>4</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="AH45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ45" t="n">
         <v>1.22</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['76', '89']</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.91</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45792.6875</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="M46" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="N46" t="n">
-        <v>1.29</v>
+        <v>2.55</v>
       </c>
       <c r="O46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
         <v>1.22</v>
       </c>
-      <c r="S46" t="n">
-        <v>4</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.67</v>
-      </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W46" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="X46" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>5.75</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.65</v>
+        <v>1.13</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6408,20 +6408,20 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['53', '90+5']</t>
+          <t>['76', '89']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>3.4</v>
+        <v>1.48</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AI46" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45792.6875</v>
@@ -6577,75 +6577,75 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
         <v>2</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P48" t="n">
         <v>2</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N48" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q48" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S48" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T48" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W48" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="X48" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AA48" t="n">
         <v>4.2</v>
@@ -6654,32 +6654,32 @@
         <v>1.22</v>
       </c>
       <c r="AC48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['45', '90+7']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['23', '38']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45792.79166666666</v>
@@ -6835,25 +6835,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>2</v>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,49 +6861,49 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.65</v>
+        <v>1.76</v>
       </c>
       <c r="M50" t="n">
-        <v>2.99</v>
+        <v>3.23</v>
       </c>
       <c r="N50" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="O50" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="R50" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S50" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T50" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U50" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W50" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="X50" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AA50" t="n">
         <v>4.2</v>
@@ -6912,32 +6912,32 @@
         <v>1.22</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
+          <t>['23', '38']</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>['45', '90+7']</t>
-        </is>
-      </c>
       <c r="AG50" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.42</v>
+        <v>2.15</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45792.79166666666</v>
@@ -7093,25 +7093,25 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G52" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" t="n">
         <v>2</v>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,83 +7119,83 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="M52" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N52" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="O52" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD52" t="n">
         <v>1.53</v>
       </c>
-      <c r="P52" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>13</v>
-      </c>
-      <c r="R52" t="n">
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>['8', '25', '45+5', '51', '88', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>['11', '21']</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AI52" t="n">
         <v>1.29</v>
       </c>
-      <c r="S52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>['10', '54']</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH52" t="n">
+      <c r="AJ52" t="n">
         <v>4.75</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>6</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45792.89583333334</v>
@@ -7222,109 +7222,109 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M53" t="n">
         <v>6</v>
       </c>
-      <c r="H53" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3</v>
-      </c>
-      <c r="J53" t="n">
-        <v>2</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M53" t="n">
-        <v>3.92</v>
-      </c>
       <c r="N53" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="O53" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="P53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>13</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T53" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q53" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S53" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T53" t="n">
-        <v>3</v>
-      </c>
       <c r="U53" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V53" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W53" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="X53" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.96</v>
+        <v>1.55</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.85</v>
+        <v>2.55</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['8', '25', '45+5', '51', '88', '90+4']</t>
+          <t>['10', '54']</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['11', '21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.95</v>
+        <v>4.75</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AJ53" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45792.89583333334</v>
